--- a/fundraiser_forms/013_fundraiser_check_in_form--fundraiser_forms.xlsx
+++ b/fundraiser_forms/013_fundraiser_check_in_form--fundraiser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fundraiser_check_in_form_1</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>check_in_status</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Check In Status</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number_of_guests</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Number of Guests</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fundraiser_check_in_form_8</t>
+          <t>number_of_volunteers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check In Status</t>
+          <t>Number of Volunteers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fundraiser_check_in_form_9</t>
+          <t>event_code</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Event Code</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fundraiser_check_in_form_10</t>
+          <t>check_in_location</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Number of Guests</t>
+          <t>Check In Location</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fundraiser_check_in_form_11</t>
+          <t>check_in_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Number of Volunteers</t>
+          <t>Check In Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,205 +745,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fundraiser_check_in_form_12</t>
+          <t>check_in_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Event Code</t>
+          <t>Check In Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>fundraiser_check_in_form_13</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Check In Location</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>fundraiser_check_in_form_14</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Check In Status Time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>fundraiser_check_in_form_15</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Check In Status Date</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>fundraiser_check_in_form_16</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Check In Status</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>fundraiser_check_in_form_17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Number of Guests</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>fundraiser_check_in_form_18</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Number of Volunteers</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>fundraiser_check_in_form_19</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Event Code</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>fundraiser_check_in_form_20</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Check In Location</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -960,10 +776,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
@@ -988,7 +804,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fundraiser_check_in_form_8_choices</t>
+          <t>check_in_status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1005,7 +821,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fundraiser_check_in_form_8_choices</t>
+          <t>check_in_status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1022,7 +838,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fundraiser_check_in_form_8_choices</t>
+          <t>check_in_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1031,57 +847,6 @@
         </is>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>Left Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>fundraiser_check_in_form_16_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>checked_in</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Checked In</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>fundraiser_check_in_form_16_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>not_checked_in</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Not Checked In</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>fundraiser_check_in_form_16_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>left_early</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
         <is>
           <t>Left Early</t>
         </is>
